--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.87669619114052</v>
+        <v>7.942463131060336</v>
       </c>
       <c r="D2" t="n">
-        <v>45.37313497088418</v>
+        <v>7.37313443276868</v>
       </c>
       <c r="E2" t="n">
-        <v>15.45111537012545</v>
+        <v>2.510806247645386</v>
       </c>
       <c r="F2" t="n">
-        <v>13.07614175231604</v>
+        <v>2.124873034751357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.76524472080448</v>
+        <v>9.386852267130729</v>
       </c>
       <c r="D3" t="n">
-        <v>55.54253895218067</v>
+        <v>9.02566257972936</v>
       </c>
       <c r="E3" t="n">
-        <v>15.45111537012545</v>
+        <v>2.510806247645386</v>
       </c>
       <c r="F3" t="n">
-        <v>13.07614175231604</v>
+        <v>2.124873034751357</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.40263570005094</v>
+        <v>2.827928301258278</v>
       </c>
       <c r="D4" t="n">
-        <v>19.74315604360085</v>
+        <v>3.208262857085138</v>
       </c>
       <c r="E4" t="n">
-        <v>15.45111537012545</v>
+        <v>2.510806247645386</v>
       </c>
       <c r="F4" t="n">
-        <v>13.07614175231604</v>
+        <v>2.124873034751357</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.93967657834542</v>
+        <v>8.115197443981131</v>
       </c>
       <c r="D5" t="n">
-        <v>42.31906851559292</v>
+        <v>6.876848633783849</v>
       </c>
       <c r="E5" t="n">
-        <v>15.45111537012545</v>
+        <v>2.510806247645386</v>
       </c>
       <c r="F5" t="n">
-        <v>13.07614175231604</v>
+        <v>2.124873034751357</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
